--- a/mapa_interactivo_Optical_Power.xlsx
+++ b/mapa_interactivo_Optical_Power.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,76 +413,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Caso</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>F. De Reclamo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Direccion</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Comuna</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>OT</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Proveedor Asignado</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Attachments</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>API_Response</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Coordenada_X</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Coordenada_Y</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Operacion</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Zona</t>
         </is>
@@ -503,26 +491,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8361</t>
+          <t>8415</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2/18/2026</t>
+          <t>2/27/2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MORAN, PEDRO 2279</t>
+          <t>CULPINA 3308</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02916347 </t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3032071</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,49 +530,47 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 2279, "cod_calle": 13123, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.489210", "y": "-34.588349"}, "direccion": "MORAN, PEDRO 2279, CABA", "nombre_calle": "MORAN, PEDRO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 3308, "cod_calle": 3203, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.435265", "y": "-34.660130"}, "direccion": "CULPINA 3308, CABA", "nombre_calle": "CULPINA", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>-58.48921</v>
+        <v>-58.435265</v>
       </c>
       <c r="L2" t="n">
-        <v>-34.588349</v>
+        <v>-34.66013</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S01007234</t>
+          <t>8426</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2/25/2026</t>
+          <t>2/27/2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>24 DE NOVIEMBRE 2151</t>
+          <t>PATAGONES 2930</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>4</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
+      <c r="E3" t="n">
+        <v>3032045</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -608,14 +592,14 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 2151, "cod_calle": 23025, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.409266", "y": "-34.636061"}, "direccion": "24 DE NOVIEMBRE 2151, CABA", "nombre_calle": "24 DE NOVIEMBRE", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 2930, "cod_calle": 17032, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.404195", "y": "-34.638148"}, "direccion": "PATAGONES 2930, CABA", "nombre_calle": "PATAGONES", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>-58.409266</v>
+        <v>-58.404195</v>
       </c>
       <c r="L3" t="n">
-        <v>-34.636061</v>
+        <v>-34.638148</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -631,26 +615,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8394</t>
+          <t>S00142199</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2/26/2026</t>
+          <t>3/4/2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MORAN, PEDRO 2845</t>
+          <t>DON BOSCO 3507</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3210819</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -664,7 +646,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>cable en panza</t>
+          <t>cables en panza verificar si estan muertos</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -672,49 +654,47 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 2845, "cod_calle": 13123, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.495695", "y": "-34.592360"}, "direccion": "MORAN, PEDRO 2845, CABA", "nombre_calle": "MORAN, PEDRO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 3507, "cod_calle": 4084, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.415576", "y": "-34.611893"}, "direccion": "DON BOSCO 3507, CABA", "nombre_calle": "DON BOSCO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-58.495695</v>
+        <v>-58.415576</v>
       </c>
       <c r="L4" t="n">
-        <v>-34.59236</v>
+        <v>-34.611893</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8396</t>
+          <t>S00201659</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2/26/2026</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MORAN, PEDRO 2955</t>
+          <t>BENEDETTI, OSVALDO E., DIP.NAC. 262</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3202029</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -728,7 +708,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>cable en panza</t>
+          <t>cables en panza</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -736,18 +716,18 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 2955, "cod_calle": 13123, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.496932", "y": "-34.593124"}, "direccion": "MORAN, PEDRO 2955, CABA", "nombre_calle": "MORAN, PEDRO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 262, "cod_calle": 12031, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.481908", "y": "-34.637868"}, "direccion": "BENEDETTI, OSVALDO E., DIP.NAC. 262, CABA", "nombre_calle": "BENEDETTI, OSVALDO E., DIP.NAC.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>-58.496932</v>
+        <v>-58.481908</v>
       </c>
       <c r="L5" t="n">
-        <v>-34.593124</v>
+        <v>-34.637868</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -759,26 +739,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8415</t>
+          <t>S00214196</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2/27/2026</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CULPINA 3308</t>
+          <t>LOPE DE VEGA 309</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3213493</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -792,7 +770,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>cable en panza</t>
+          <t>cables en panza</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -800,49 +778,47 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 3308, "cod_calle": 3203, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.435265", "y": "-34.660130"}, "direccion": "CULPINA 3308, CABA", "nombre_calle": "CULPINA", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 309, "cod_calle": 12126, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.499903", "y": "-34.635003"}, "direccion": "LOPE DE VEGA 309, CABA", "nombre_calle": "LOPE DE VEGA", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-58.435265</v>
+        <v>-58.499903</v>
       </c>
       <c r="L6" t="n">
-        <v>-34.66013</v>
+        <v>-34.635003</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8426</t>
+          <t>8444</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2/27/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PATAGONES 2930</t>
+          <t>BUCARELLI 1305</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
+        <v>15</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3215700</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -864,23 +840,147 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 2930, "cod_calle": 17032, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.404195", "y": "-34.638148"}, "direccion": "PATAGONES 2930, CABA", "nombre_calle": "PATAGONES", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 1305, "cod_calle": 2121, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.479078", "y": "-34.586298"}, "direccion": "BUCARELLI 1305, CABA", "nombre_calle": "BUCARELLI", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-58.404195</v>
+        <v>-58.479078</v>
       </c>
       <c r="L7" t="n">
-        <v>-34.638148</v>
+        <v>-34.586298</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>8445</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>3/9/2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DE LOS INCAS AV. 4755</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3215803</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>cable en panza</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 4755, "cod_calle": 4045, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.477390", "y": "-34.583509"}, "direccion": "DE LOS INCAS AV. 4755, CABA", "nombre_calle": "DE LOS INCAS AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>-58.47739</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-34.583509</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8462  </t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>3/10/2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ANDONAEGUI 1668</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>15</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3216113</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Normalizar cable caido</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 1668, "cod_calle": 1082, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.483678", "y": "-34.583424"}, "direccion": "ANDONAEGUI 1668, CABA", "nombre_calle": "ANDONAEGUI", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>-58.483678</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-34.583424</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
         </is>
       </c>
     </row>

--- a/mapa_interactivo_Optical_Power.xlsx
+++ b/mapa_interactivo_Optical_Power.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,24 +491,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8415</t>
+          <t>S00142199</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2/27/2026</t>
+          <t>3/4/2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CULPINA 3308</t>
+          <t>DON BOSCO 3507</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>3032071</v>
+        <v>3210819</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -522,7 +522,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>cable en panza</t>
+          <t>cables en panza verificar si estan muertos</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -530,18 +530,18 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 3308, "cod_calle": 3203, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.435265", "y": "-34.660130"}, "direccion": "CULPINA 3308, CABA", "nombre_calle": "CULPINA", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 3507, "cod_calle": 4084, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.415576", "y": "-34.611893"}, "direccion": "DON BOSCO 3507, CABA", "nombre_calle": "DON BOSCO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>-58.435265</v>
+        <v>-58.415576</v>
       </c>
       <c r="L2" t="n">
-        <v>-34.66013</v>
+        <v>-34.611893</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -553,24 +553,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8426</t>
+          <t>S00201659</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2/27/2026</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PATAGONES 2930</t>
+          <t>BENEDETTI, OSVALDO E., DIP.NAC. 262</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>3032045</v>
+        <v>3202029</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -584,7 +584,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>cable en panza</t>
+          <t>cables en panza</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -592,47 +592,47 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 2930, "cod_calle": 17032, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.404195", "y": "-34.638148"}, "direccion": "PATAGONES 2930, CABA", "nombre_calle": "PATAGONES", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 262, "cod_calle": 12031, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.481908", "y": "-34.637868"}, "direccion": "BENEDETTI, OSVALDO E., DIP.NAC. 262, CABA", "nombre_calle": "BENEDETTI, OSVALDO E., DIP.NAC.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>-58.404195</v>
+        <v>-58.481908</v>
       </c>
       <c r="L3" t="n">
-        <v>-34.638148</v>
+        <v>-34.637868</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S00142199</t>
+          <t>S00214196</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3/4/2026</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DON BOSCO 3507</t>
+          <t>LOPE DE VEGA 309</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>3210819</v>
+        <v>3213493</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>cables en panza verificar si estan muertos</t>
+          <t>cables en panza</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -654,47 +654,47 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 3507, "cod_calle": 4084, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.415576", "y": "-34.611893"}, "direccion": "DON BOSCO 3507, CABA", "nombre_calle": "DON BOSCO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 309, "cod_calle": 12126, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.499903", "y": "-34.635003"}, "direccion": "LOPE DE VEGA 309, CABA", "nombre_calle": "LOPE DE VEGA", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-58.415576</v>
+        <v>-58.499903</v>
       </c>
       <c r="L4" t="n">
-        <v>-34.611893</v>
+        <v>-34.635003</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S00201659</t>
+          <t>8444</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BENEDETTI, OSVALDO E., DIP.NAC. 262</t>
+          <t>BUCARELLI 1305</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>3202029</v>
+        <v>3215700</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>cables en panza</t>
+          <t>cable en panza</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -716,18 +716,18 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 262, "cod_calle": 12031, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.481908", "y": "-34.637868"}, "direccion": "BENEDETTI, OSVALDO E., DIP.NAC. 262, CABA", "nombre_calle": "BENEDETTI, OSVALDO E., DIP.NAC.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 1305, "cod_calle": 2121, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.479078", "y": "-34.586298"}, "direccion": "BUCARELLI 1305, CABA", "nombre_calle": "BUCARELLI", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>-58.481908</v>
+        <v>-58.479078</v>
       </c>
       <c r="L5" t="n">
-        <v>-34.637868</v>
+        <v>-34.586298</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -739,24 +739,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S00214196</t>
+          <t>8445</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LOPE DE VEGA 309</t>
+          <t>DE LOS INCAS AV. 4755</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>3213493</v>
+        <v>3215803</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>cables en panza</t>
+          <t>cable en panza</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -778,18 +778,18 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 309, "cod_calle": 12126, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.499903", "y": "-34.635003"}, "direccion": "LOPE DE VEGA 309, CABA", "nombre_calle": "LOPE DE VEGA", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 4755, "cod_calle": 4045, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.477390", "y": "-34.583509"}, "direccion": "DE LOS INCAS AV. 4755, CABA", "nombre_calle": "DE LOS INCAS AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-58.499903</v>
+        <v>-58.47739</v>
       </c>
       <c r="L6" t="n">
-        <v>-34.635003</v>
+        <v>-34.583509</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -801,24 +801,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8444</t>
+          <t xml:space="preserve">8462  </t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>3/10/2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BUCARELLI 1305</t>
+          <t>ANDONAEGUI 1668</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>3215700</v>
+        <v>3216113</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>cable en panza</t>
+          <t>Normalizar cable caido</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -840,14 +840,14 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 1305, "cod_calle": 2121, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.479078", "y": "-34.586298"}, "direccion": "BUCARELLI 1305, CABA", "nombre_calle": "BUCARELLI", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 1668, "cod_calle": 1082, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.483678", "y": "-34.583424"}, "direccion": "ANDONAEGUI 1668, CABA", "nombre_calle": "ANDONAEGUI", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-58.479078</v>
+        <v>-58.483678</v>
       </c>
       <c r="L7" t="n">
-        <v>-34.586298</v>
+        <v>-34.583424</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -855,130 +855,6 @@
         </is>
       </c>
       <c r="N7" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>8445</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3/9/2026</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>DE LOS INCAS AV. 4755</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>15</v>
-      </c>
-      <c r="E8" t="n">
-        <v>3215803</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>cable en panza</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>{"direccionesNormalizadas": [{"altura": 4755, "cod_calle": 4045, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.477390", "y": "-34.583509"}, "direccion": "DE LOS INCAS AV. 4755, CABA", "nombre_calle": "DE LOS INCAS AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>-58.47739</v>
-      </c>
-      <c r="L8" t="n">
-        <v>-34.583509</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Paternal</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8462  </t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3/10/2026</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ANDONAEGUI 1668</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>15</v>
-      </c>
-      <c r="E9" t="n">
-        <v>3216113</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Normalizar cable caido</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>{"direccionesNormalizadas": [{"altura": 1668, "cod_calle": 1082, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.483678", "y": "-34.583424"}, "direccion": "ANDONAEGUI 1668, CABA", "nombre_calle": "ANDONAEGUI", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>-58.483678</v>
-      </c>
-      <c r="L9" t="n">
-        <v>-34.583424</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Paternal</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
         <is>
           <t>Capital Norte</t>
         </is>

--- a/mapa_interactivo_Optical_Power.xlsx
+++ b/mapa_interactivo_Optical_Power.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,6 +860,538 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>00246013</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>3/19/2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>FERNANDEZ 598</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Red Baja Altura</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 598, "cod_calle": 6012, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.483332", "y": "-34.641961"}, "direccion": "FERNANDEZ 598, CABA", "nombre_calle": "FERNANDEZ", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>-58.483332</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-34.641961</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Devoto</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>00189037</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>3/19/2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>JUSTO JUAN B AV 7524</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Red Baja Altura</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 7524, "cod_calle": 10018, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.495106", "y": "-34.629846"}, "direccion": "JUSTO, JUAN B. AV. 7524, CABA", "nombre_calle": "JUSTO, JUAN B. AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>-58.495106</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-34.629846</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Devoto</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>R002</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>3/20/2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CUBAS JOSE 2701 CABA , caba</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>REUBICAR CDO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>No ubicado</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>No clasificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>00506042</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NEUQUEN 2765</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>NORMALIZAR RED CABLES BAJOS Y EN DESUSO.</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 2765, "cod_calle": 14017, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.472080", "y": "-34.620583"}, "direccion": "NEUQUEN 2765, CABA", "nombre_calle": "NEUQUEN", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>-58.47208</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-34.620583</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>00147974</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CAMINO MIGUEL ANDRES 3710</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NORMALIZAR RED A BAJA ALTURA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 3710, "cod_calle": 3037, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.501857", "y": "-34.564503"}, "direccion": "CAMINO, MIGUEL ANDRÉS 3710, CABA", "nombre_calle": "CAMINO, MIGUEL ANDRÉS", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>-58.501857</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-34.564503</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>00237347</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>FOREST AV 731</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>15</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>NORMALIZAR RED A BAJA ALTURA Y DESMONTAR CABLES EN DESUSO.</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 731, "cod_calle": 6040, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.455383", "y": "-34.583497"}, "direccion": "FOREST AV. 731, CABA", "nombre_calle": "FOREST AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>-58.455383</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-34.583497</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Colegiales</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>8651</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>UNANUE 5888</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>8</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>CABLES FUERA DE NORMA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 5888, "cod_calle": 22006, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.473602", "y": "-34.680706"}, "direccion": "UNANUE 5888, CABA", "nombre_calle": "UNANUE", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>-58.473602</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-34.680706</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>8672</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>TINOGASTA 4558</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>CABLES FUERA DE NORMA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 4558, "cod_calle": 21032, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.510948", "y": "-34.609681"}, "direccion": "TINOGASTA 4558, CABA", "nombre_calle": "TINOGASTA", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>-58.510948</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-34.609681</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Devoto</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>00297697</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BELAUSTEGUI LUIS DR 4550</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>NORMALIZAR CABLES FUERA DE NORMA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 4550, "cod_calle": 2046, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.493912", "y": "-34.627948"}, "direccion": "BELAUSTEGUI, LUIS, DR. 4550, CABA", "nombre_calle": "BELAUSTEGUI, LUIS, DR.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>-58.493912</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-34.627948</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Devoto</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapa_interactivo_Optical_Power.xlsx
+++ b/mapa_interactivo_Optical_Power.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,24 +491,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S00142199</t>
+          <t>S00201659</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3/4/2026</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DON BOSCO 3507</t>
+          <t>BENEDETTI, OSVALDO E., DIP.NAC. 262</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>3210819</v>
+        <v>3202029</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -522,7 +522,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>cables en panza verificar si estan muertos</t>
+          <t>cables en panza</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -530,30 +530,30 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 3507, "cod_calle": 4084, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.415576", "y": "-34.611893"}, "direccion": "DON BOSCO 3507, CABA", "nombre_calle": "DON BOSCO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 262, "cod_calle": 12031, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.481908", "y": "-34.637868"}, "direccion": "BENEDETTI, OSVALDO E., DIP.NAC. 262, CABA", "nombre_calle": "BENEDETTI, OSVALDO E., DIP.NAC.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>-58.415576</v>
+        <v>-58.481908</v>
       </c>
       <c r="L2" t="n">
-        <v>-34.611893</v>
+        <v>-34.637868</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S00201659</t>
+          <t>S00214196</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -563,14 +563,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BENEDETTI, OSVALDO E., DIP.NAC. 262</t>
+          <t>LOPE DE VEGA 309</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>3202029</v>
+        <v>3213493</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -592,14 +592,14 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 262, "cod_calle": 12031, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.481908", "y": "-34.637868"}, "direccion": "BENEDETTI, OSVALDO E., DIP.NAC. 262, CABA", "nombre_calle": "BENEDETTI, OSVALDO E., DIP.NAC.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 309, "cod_calle": 12126, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.499903", "y": "-34.635003"}, "direccion": "LOPE DE VEGA 309, CABA", "nombre_calle": "LOPE DE VEGA", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>-58.481908</v>
+        <v>-58.499903</v>
       </c>
       <c r="L3" t="n">
-        <v>-34.637868</v>
+        <v>-34.635003</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -615,24 +615,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S00214196</t>
+          <t>8444</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LOPE DE VEGA 309</t>
+          <t>BUCARELLI 1305</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>3213493</v>
+        <v>3215700</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>cables en panza</t>
+          <t>cable en panza</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -654,18 +654,18 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 309, "cod_calle": 12126, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.499903", "y": "-34.635003"}, "direccion": "LOPE DE VEGA 309, CABA", "nombre_calle": "LOPE DE VEGA", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 1305, "cod_calle": 2121, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.479078", "y": "-34.586298"}, "direccion": "BUCARELLI 1305, CABA", "nombre_calle": "BUCARELLI", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-58.499903</v>
+        <v>-58.479078</v>
       </c>
       <c r="L4" t="n">
-        <v>-34.635003</v>
+        <v>-34.586298</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -677,7 +677,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8444</t>
+          <t>8445</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -687,14 +687,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BUCARELLI 1305</t>
+          <t>DE LOS INCAS AV. 4755</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>3215700</v>
+        <v>3215803</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -716,14 +716,14 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 1305, "cod_calle": 2121, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.479078", "y": "-34.586298"}, "direccion": "BUCARELLI 1305, CABA", "nombre_calle": "BUCARELLI", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 4755, "cod_calle": 4045, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.477390", "y": "-34.583509"}, "direccion": "DE LOS INCAS AV. 4755, CABA", "nombre_calle": "DE LOS INCAS AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>-58.479078</v>
+        <v>-58.47739</v>
       </c>
       <c r="L5" t="n">
-        <v>-34.586298</v>
+        <v>-34.583509</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -739,24 +739,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8445</t>
+          <t xml:space="preserve">8462  </t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>3/10/2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DE LOS INCAS AV. 4755</t>
+          <t>ANDONAEGUI 1668</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>3215803</v>
+        <v>3216113</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>cable en panza</t>
+          <t>Normalizar cable caido</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -778,14 +778,14 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 4755, "cod_calle": 4045, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.477390", "y": "-34.583509"}, "direccion": "DE LOS INCAS AV. 4755, CABA", "nombre_calle": "DE LOS INCAS AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 1668, "cod_calle": 1082, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.483678", "y": "-34.583424"}, "direccion": "ANDONAEGUI 1668, CABA", "nombre_calle": "ANDONAEGUI", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-58.47739</v>
+        <v>-58.483678</v>
       </c>
       <c r="L6" t="n">
-        <v>-34.583509</v>
+        <v>-34.583424</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -801,25 +801,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">8462  </t>
+          <t>00246013</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3/10/2026</t>
+          <t>3/19/2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ANDONAEGUI 1668</t>
+          <t>FERNANDEZ 598</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3216113</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>Optical Power</t>
@@ -832,7 +830,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Normalizar cable caido</t>
+          <t>Red Baja Altura</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -840,18 +838,18 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 1668, "cod_calle": 1082, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.483678", "y": "-34.583424"}, "direccion": "ANDONAEGUI 1668, CABA", "nombre_calle": "ANDONAEGUI", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 598, "cod_calle": 6012, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.483332", "y": "-34.641961"}, "direccion": "FERNANDEZ 598, CABA", "nombre_calle": "FERNANDEZ", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-58.483678</v>
+        <v>-58.483332</v>
       </c>
       <c r="L7" t="n">
-        <v>-34.583424</v>
+        <v>-34.641961</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -863,7 +861,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00246013</t>
+          <t>00189037</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -873,11 +871,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FERNANDEZ 598</t>
+          <t>JUSTO JUAN B AV 7524</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
@@ -900,14 +898,14 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 598, "cod_calle": 6012, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.483332", "y": "-34.641961"}, "direccion": "FERNANDEZ 598, CABA", "nombre_calle": "FERNANDEZ", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 7524, "cod_calle": 10018, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.495106", "y": "-34.629846"}, "direccion": "JUSTO, JUAN B. AV. 7524, CABA", "nombre_calle": "JUSTO, JUAN B. AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-58.483332</v>
+        <v>-58.495106</v>
       </c>
       <c r="L8" t="n">
-        <v>-34.641961</v>
+        <v>-34.629846</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -923,21 +921,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>00189037</t>
+          <t>R002</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3/19/2026</t>
+          <t>3/20/2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>JUSTO JUAN B AV 7524</t>
+          <t>CUBAS JOSE 2701 CABA , caba</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
@@ -952,52 +950,44 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Red Baja Altura</t>
+          <t>REUBICAR CDO</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>{"direccionesNormalizadas": [{"altura": 7524, "cod_calle": 10018, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.495106", "y": "-34.629846"}, "direccion": "JUSTO, JUAN B. AV. 7524, CABA", "nombre_calle": "JUSTO, JUAN B. AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>-58.495106</v>
-      </c>
-      <c r="L9" t="n">
-        <v>-34.629846</v>
-      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>No ubicado</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>No clasificado</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R002</t>
+          <t>00506042</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3/20/2026</t>
+          <t>3/21/2026</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CUBAS JOSE 2701 CABA , caba</t>
+          <t>NEUQUEN 2765</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
@@ -1012,30 +1002,38 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>REUBICAR CDO</t>
+          <t>NORMALIZAR RED CABLES BAJOS Y EN DESUSO.</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 2765, "cod_calle": 14017, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.472080", "y": "-34.620583"}, "direccion": "NEUQUEN 2765, CABA", "nombre_calle": "NEUQUEN", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>-58.47208</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-34.620583</v>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>No ubicado</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>No clasificado</t>
+          <t>Capital Norte</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>00506042</t>
+          <t>00147974</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1045,11 +1043,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NEUQUEN 2765</t>
+          <t>CAMINO MIGUEL ANDRES 3710</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
@@ -1064,7 +1062,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>NORMALIZAR RED CABLES BAJOS Y EN DESUSO.</t>
+          <t>NORMALIZAR RED A BAJA ALTURA</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1072,14 +1070,14 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 2765, "cod_calle": 14017, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.472080", "y": "-34.620583"}, "direccion": "NEUQUEN 2765, CABA", "nombre_calle": "NEUQUEN", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 3710, "cod_calle": 3037, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.501857", "y": "-34.564503"}, "direccion": "CAMINO, MIGUEL ANDRÉS 3710, CABA", "nombre_calle": "CAMINO, MIGUEL ANDRÉS", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>-58.47208</v>
+        <v>-58.501857</v>
       </c>
       <c r="L11" t="n">
-        <v>-34.620583</v>
+        <v>-34.564503</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1095,7 +1093,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>00147974</t>
+          <t>00237347</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1105,11 +1103,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CAMINO MIGUEL ANDRES 3710</t>
+          <t>FOREST AV 731</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
@@ -1124,7 +1122,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>NORMALIZAR RED A BAJA ALTURA</t>
+          <t>NORMALIZAR RED A BAJA ALTURA Y DESMONTAR CABLES EN DESUSO.</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1132,18 +1130,18 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 3710, "cod_calle": 3037, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.501857", "y": "-34.564503"}, "direccion": "CAMINO, MIGUEL ANDRÉS 3710, CABA", "nombre_calle": "CAMINO, MIGUEL ANDRÉS", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 731, "cod_calle": 6040, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.455383", "y": "-34.583497"}, "direccion": "FOREST AV. 731, CABA", "nombre_calle": "FOREST AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-58.501857</v>
+        <v>-58.455383</v>
       </c>
       <c r="L12" t="n">
-        <v>-34.564503</v>
+        <v>-34.583497</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1155,7 +1153,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>00237347</t>
+          <t>8651</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1165,11 +1163,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FOREST AV 731</t>
+          <t>UNANUE 5888</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
@@ -1184,7 +1182,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>NORMALIZAR RED A BAJA ALTURA Y DESMONTAR CABLES EN DESUSO.</t>
+          <t>CABLES FUERA DE NORMA</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1192,30 +1190,30 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 731, "cod_calle": 6040, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.455383", "y": "-34.583497"}, "direccion": "FOREST AV. 731, CABA", "nombre_calle": "FOREST AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 5888, "cod_calle": 22006, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.473602", "y": "-34.680706"}, "direccion": "UNANUE 5888, CABA", "nombre_calle": "UNANUE", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-58.455383</v>
+        <v>-58.473602</v>
       </c>
       <c r="L13" t="n">
-        <v>-34.583497</v>
+        <v>-34.680706</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8651</t>
+          <t>8672</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1225,11 +1223,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UNANUE 5888</t>
+          <t>TINOGASTA 4558</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
@@ -1252,30 +1250,30 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 5888, "cod_calle": 22006, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.473602", "y": "-34.680706"}, "direccion": "UNANUE 5888, CABA", "nombre_calle": "UNANUE", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 4558, "cod_calle": 21032, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.510948", "y": "-34.609681"}, "direccion": "TINOGASTA 4558, CABA", "nombre_calle": "TINOGASTA", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>-58.473602</v>
+        <v>-58.510948</v>
       </c>
       <c r="L14" t="n">
-        <v>-34.680706</v>
+        <v>-34.609681</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8672</t>
+          <t>00297697</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1285,11 +1283,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TINOGASTA 4558</t>
+          <t>BELAUSTEGUI LUIS DR 4550</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
@@ -1304,7 +1302,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>CABLES FUERA DE NORMA</t>
+          <t>NORMALIZAR CABLES FUERA DE NORMA</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1312,14 +1310,14 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 4558, "cod_calle": 21032, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.510948", "y": "-34.609681"}, "direccion": "TINOGASTA 4558, CABA", "nombre_calle": "TINOGASTA", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 4550, "cod_calle": 2046, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.493912", "y": "-34.627948"}, "direccion": "BELAUSTEGUI, LUIS, DR. 4550, CABA", "nombre_calle": "BELAUSTEGUI, LUIS, DR.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>-58.510948</v>
+        <v>-58.493912</v>
       </c>
       <c r="L15" t="n">
-        <v>-34.609681</v>
+        <v>-34.627948</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1335,21 +1333,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>00297697</t>
+          <t>00297920</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3/21/2026</t>
+          <t>3/22/2026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BELAUSTEGUI LUIS DR 4550</t>
+          <t>MOLDES 1957</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
@@ -1364,7 +1362,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>NORMALIZAR CABLES FUERA DE NORMA</t>
+          <t>NORMALIZAR RED A BAJA ALTURA</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1372,21 +1370,141 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 4550, "cod_calle": 2046, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.493912", "y": "-34.627948"}, "direccion": "BELAUSTEGUI, LUIS, DR. 4550, CABA", "nombre_calle": "BELAUSTEGUI, LUIS, DR.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 1957, "cod_calle": 13099, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.458285", "y": "-34.564964"}, "direccion": "MOLDES 1957, CABA", "nombre_calle": "MOLDES", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>-58.493912</v>
+        <v>-58.458285</v>
       </c>
       <c r="L16" t="n">
-        <v>-34.627948</v>
+        <v>-34.564964</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>00299285</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>3/27/2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MATORRAS 247</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 247, "cod_calle": 13050, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.431280", "y": "-34.623327"}, "direccion": "MATORRAS 247, CABA", "nombre_calle": "MATORRAS", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>-58.43128</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-34.623327</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>00203594</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>3/28/2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CRAMER 4061</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 4061, "cod_calle": 3189, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.475268", "y": "-34.547194"}, "direccion": "CRAMER 4061, CABA", "nombre_calle": "CRAMER", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>-58.475268</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-34.547194</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>Capital Norte</t>
         </is>

--- a/mapa_interactivo_Optical_Power.xlsx
+++ b/mapa_interactivo_Optical_Power.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,25 +491,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S00201659</t>
+          <t>R002</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>3/20/2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BENEDETTI, OSVALDO E., DIP.NAC. 262</t>
+          <t>CUBAS JOSE 2701 CABA , caba</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E2" t="n">
-        <v>3202029</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Optical Power</t>
@@ -522,56 +520,46 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>cables en panza</t>
+          <t>REUBICAR CDO</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>{"direccionesNormalizadas": [{"altura": 262, "cod_calle": 12031, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.481908", "y": "-34.637868"}, "direccion": "BENEDETTI, OSVALDO E., DIP.NAC. 262, CABA", "nombre_calle": "BENEDETTI, OSVALDO E., DIP.NAC.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>-58.481908</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-34.637868</v>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>No ubicado</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>No clasificado</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S00214196</t>
+          <t>00147974</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>3/21/2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LOPE DE VEGA 309</t>
+          <t>CAMINO MIGUEL ANDRES 3710</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E3" t="n">
-        <v>3213493</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>Optical Power</t>
@@ -584,7 +572,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>cables en panza</t>
+          <t>NORMALIZAR RED A BAJA ALTURA</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -592,18 +580,18 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 309, "cod_calle": 12126, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.499903", "y": "-34.635003"}, "direccion": "LOPE DE VEGA 309, CABA", "nombre_calle": "LOPE DE VEGA", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 3710, "cod_calle": 3037, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.501857", "y": "-34.564503"}, "direccion": "CAMINO, MIGUEL ANDRÉS 3710, CABA", "nombre_calle": "CAMINO, MIGUEL ANDRÉS", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>-58.499903</v>
+        <v>-58.501857</v>
       </c>
       <c r="L3" t="n">
-        <v>-34.635003</v>
+        <v>-34.564503</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -615,25 +603,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8444</t>
+          <t>8672</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>3/21/2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BUCARELLI 1305</t>
+          <t>TINOGASTA 4558</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3215700</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>Optical Power</t>
@@ -646,7 +632,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>cable en panza</t>
+          <t>CABLES FUERA DE NORMA</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -654,18 +640,18 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 1305, "cod_calle": 2121, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.479078", "y": "-34.586298"}, "direccion": "BUCARELLI 1305, CABA", "nombre_calle": "BUCARELLI", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 4558, "cod_calle": 21032, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.510948", "y": "-34.609681"}, "direccion": "TINOGASTA 4558, CABA", "nombre_calle": "TINOGASTA", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-58.479078</v>
+        <v>-58.510948</v>
       </c>
       <c r="L4" t="n">
-        <v>-34.586298</v>
+        <v>-34.609681</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -677,25 +663,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8445</t>
+          <t>00297697</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>3/21/2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DE LOS INCAS AV. 4755</t>
+          <t>BELAUSTEGUI LUIS DR 4550</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3215803</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Optical Power</t>
@@ -708,7 +692,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>cable en panza</t>
+          <t>NORMALIZAR CABLES FUERA DE NORMA</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -716,18 +700,18 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 4755, "cod_calle": 4045, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.477390", "y": "-34.583509"}, "direccion": "DE LOS INCAS AV. 4755, CABA", "nombre_calle": "DE LOS INCAS AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 4550, "cod_calle": 2046, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.493912", "y": "-34.627948"}, "direccion": "BELAUSTEGUI, LUIS, DR. 4550, CABA", "nombre_calle": "BELAUSTEGUI, LUIS, DR.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>-58.47739</v>
+        <v>-58.493912</v>
       </c>
       <c r="L5" t="n">
-        <v>-34.583509</v>
+        <v>-34.627948</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -739,25 +723,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">8462  </t>
+          <t>00297920</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3/10/2026</t>
+          <t>3/22/2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ANDONAEGUI 1668</t>
+          <t>MOLDES 1957</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3216113</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>Optical Power</t>
@@ -770,7 +752,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Normalizar cable caido</t>
+          <t>NORMALIZAR RED A BAJA ALTURA</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -778,18 +760,18 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 1668, "cod_calle": 1082, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.483678", "y": "-34.583424"}, "direccion": "ANDONAEGUI 1668, CABA", "nombre_calle": "ANDONAEGUI", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 1957, "cod_calle": 13099, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.458285", "y": "-34.564964"}, "direccion": "MOLDES 1957, CABA", "nombre_calle": "MOLDES", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-58.483678</v>
+        <v>-58.458285</v>
       </c>
       <c r="L6" t="n">
-        <v>-34.583424</v>
+        <v>-34.564964</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -801,21 +783,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00246013</t>
+          <t>00203594</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3/19/2026</t>
+          <t>3/28/2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FERNANDEZ 598</t>
+          <t>CRAMER 4061</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
@@ -830,7 +812,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Red Baja Altura</t>
+          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -838,673 +820,21 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 598, "cod_calle": 6012, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.483332", "y": "-34.641961"}, "direccion": "FERNANDEZ 598, CABA", "nombre_calle": "FERNANDEZ", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 4061, "cod_calle": 3189, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.475268", "y": "-34.547194"}, "direccion": "CRAMER 4061, CABA", "nombre_calle": "CRAMER", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-58.483332</v>
+        <v>-58.475268</v>
       </c>
       <c r="L7" t="n">
-        <v>-34.641961</v>
+        <v>-34.547194</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>00189037</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3/19/2026</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>JUSTO JUAN B AV 7524</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Red Baja Altura</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>{"direccionesNormalizadas": [{"altura": 7524, "cod_calle": 10018, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.495106", "y": "-34.629846"}, "direccion": "JUSTO, JUAN B. AV. 7524, CABA", "nombre_calle": "JUSTO, JUAN B. AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>-58.495106</v>
-      </c>
-      <c r="L8" t="n">
-        <v>-34.629846</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Devoto</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>R002</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3/20/2026</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>CUBAS JOSE 2701 CABA , caba</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>12</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>REUBICAR CDO</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>No ubicado</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>No clasificado</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>00506042</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3/21/2026</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>NEUQUEN 2765</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>7</v>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>NORMALIZAR RED CABLES BAJOS Y EN DESUSO.</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>{"direccionesNormalizadas": [{"altura": 2765, "cod_calle": 14017, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.472080", "y": "-34.620583"}, "direccion": "NEUQUEN 2765, CABA", "nombre_calle": "NEUQUEN", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>-58.47208</v>
-      </c>
-      <c r="L10" t="n">
-        <v>-34.620583</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Paternal</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>00147974</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3/21/2026</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>CAMINO MIGUEL ANDRES 3710</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>12</v>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>NORMALIZAR RED A BAJA ALTURA</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>{"direccionesNormalizadas": [{"altura": 3710, "cod_calle": 3037, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.501857", "y": "-34.564503"}, "direccion": "CAMINO, MIGUEL ANDRÉS 3710, CABA", "nombre_calle": "CAMINO, MIGUEL ANDRÉS", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>-58.501857</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-34.564503</v>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Paternal</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>00237347</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3/21/2026</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>FOREST AV 731</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>15</v>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>NORMALIZAR RED A BAJA ALTURA Y DESMONTAR CABLES EN DESUSO.</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>{"direccionesNormalizadas": [{"altura": 731, "cod_calle": 6040, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.455383", "y": "-34.583497"}, "direccion": "FOREST AV. 731, CABA", "nombre_calle": "FOREST AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>-58.455383</v>
-      </c>
-      <c r="L12" t="n">
-        <v>-34.583497</v>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Colegiales</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>8651</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3/21/2026</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>UNANUE 5888</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>8</v>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>CABLES FUERA DE NORMA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>{"direccionesNormalizadas": [{"altura": 5888, "cod_calle": 22006, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.473602", "y": "-34.680706"}, "direccion": "UNANUE 5888, CABA", "nombre_calle": "UNANUE", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>-58.473602</v>
-      </c>
-      <c r="L13" t="n">
-        <v>-34.680706</v>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>8672</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3/21/2026</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>TINOGASTA 4558</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11</v>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>CABLES FUERA DE NORMA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>{"direccionesNormalizadas": [{"altura": 4558, "cod_calle": 21032, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.510948", "y": "-34.609681"}, "direccion": "TINOGASTA 4558, CABA", "nombre_calle": "TINOGASTA", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>-58.510948</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-34.609681</v>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Devoto</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>00297697</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3/21/2026</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>BELAUSTEGUI LUIS DR 4550</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>NORMALIZAR CABLES FUERA DE NORMA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>{"direccionesNormalizadas": [{"altura": 4550, "cod_calle": 2046, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.493912", "y": "-34.627948"}, "direccion": "BELAUSTEGUI, LUIS, DR. 4550, CABA", "nombre_calle": "BELAUSTEGUI, LUIS, DR.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>-58.493912</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-34.627948</v>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Devoto</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>00297920</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3/22/2026</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>MOLDES 1957</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>12</v>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>NORMALIZAR RED A BAJA ALTURA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>{"direccionesNormalizadas": [{"altura": 1957, "cod_calle": 13099, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.458285", "y": "-34.564964"}, "direccion": "MOLDES 1957, CABA", "nombre_calle": "MOLDES", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>-58.458285</v>
-      </c>
-      <c r="L16" t="n">
-        <v>-34.564964</v>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Colegiales</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>00299285</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>3/27/2026</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>MATORRAS 247</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>6</v>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>{"direccionesNormalizadas": [{"altura": 247, "cod_calle": 13050, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.431280", "y": "-34.623327"}, "direccion": "MATORRAS 247, CABA", "nombre_calle": "MATORRAS", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>-58.43128</v>
-      </c>
-      <c r="L17" t="n">
-        <v>-34.623327</v>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>00203594</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>3/28/2026</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>CRAMER 4061</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>12</v>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>{"direccionesNormalizadas": [{"altura": 4061, "cod_calle": 3189, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.475268", "y": "-34.547194"}, "direccion": "CRAMER 4061, CABA", "nombre_calle": "CRAMER", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>-58.475268</v>
-      </c>
-      <c r="L18" t="n">
-        <v>-34.547194</v>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Saavedra</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
         <is>
           <t>Capital Norte</t>
         </is>

--- a/mapa_interactivo_Optical_Power.xlsx
+++ b/mapa_interactivo_Optical_Power.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,21 +603,21 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8672</t>
+          <t>00203594</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3/21/2026</t>
+          <t>3/28/2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TINOGASTA 4558</t>
+          <t>CRAMER 4061</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CABLES FUERA DE NORMA</t>
+          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -640,201 +640,21 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 4558, "cod_calle": 21032, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.510948", "y": "-34.609681"}, "direccion": "TINOGASTA 4558, CABA", "nombre_calle": "TINOGASTA", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 4061, "cod_calle": 3189, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.475268", "y": "-34.547194"}, "direccion": "CRAMER 4061, CABA", "nombre_calle": "CRAMER", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-58.510948</v>
+        <v>-58.475268</v>
       </c>
       <c r="L4" t="n">
-        <v>-34.609681</v>
+        <v>-34.547194</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>00297697</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>3/21/2026</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>BELAUSTEGUI LUIS DR 4550</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>NORMALIZAR CABLES FUERA DE NORMA</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>{"direccionesNormalizadas": [{"altura": 4550, "cod_calle": 2046, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.493912", "y": "-34.627948"}, "direccion": "BELAUSTEGUI, LUIS, DR. 4550, CABA", "nombre_calle": "BELAUSTEGUI, LUIS, DR.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>-58.493912</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-34.627948</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Devoto</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>00297920</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>3/22/2026</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>MOLDES 1957</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>12</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>NORMALIZAR RED A BAJA ALTURA</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>{"direccionesNormalizadas": [{"altura": 1957, "cod_calle": 13099, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.458285", "y": "-34.564964"}, "direccion": "MOLDES 1957, CABA", "nombre_calle": "MOLDES", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>-58.458285</v>
-      </c>
-      <c r="L6" t="n">
-        <v>-34.564964</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Colegiales</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>00203594</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3/28/2026</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>CRAMER 4061</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>12</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>{"direccionesNormalizadas": [{"altura": 4061, "cod_calle": 3189, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.475268", "y": "-34.547194"}, "direccion": "CRAMER 4061, CABA", "nombre_calle": "CRAMER", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>-58.475268</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-34.547194</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Saavedra</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
         <is>
           <t>Capital Norte</t>
         </is>

--- a/mapa_interactivo_Optical_Power.xlsx
+++ b/mapa_interactivo_Optical_Power.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -655,6 +655,426 @@
         </is>
       </c>
       <c r="N4" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>S00328955</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AV CALLAO 2014</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NORMALIZAR CABLES CAIDOS</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 2014, "cod_calle": 3030, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.386954", "y": "-34.587337"}, "direccion": "CALLAO AV. 2014, CABA", "nombre_calle": "CALLAO AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>-58.386954</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-34.587337</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>S00328057</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>OHIGGINS 2328</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>13</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>NORMALIZAR CABLES CAIDOS</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 2328, "cod_calle": 16009, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.454826", "y": "-34.557740"}, "direccion": "O'HIGGINS 2328, CABA", "nombre_calle": "O'HIGGINS", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>-58.454826</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-34.55774</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>S00363996</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CONGRESO 2077</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>13</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>CABLE SUELTO</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 2077, "cod_calle": 3156, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.459312", "y": "-34.553673"}, "direccion": "CONGRESO 2077, CABA", "nombre_calle": "CONGRESO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>-58.459312</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-34.553673</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>8876</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PICO 1597</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>12</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 1597, "cod_calle": 17074, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.466221", "y": "-34.536587"}, "direccion": "PICO 1597, CABA", "nombre_calle": "PICO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>-58.466221</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-34.536587</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>S00160880</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SAN MARTIN 577</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>NORMALIZAR CABLES CON MEDIA CAÑA EN FACHADA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 577, "cod_calle": 20044, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.373937", "y": "-34.601335"}, "direccion": "SAN MARTIN 577, CABA", "nombre_calle": "SAN MARTIN", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}, {"altura": 577, "cod_calle": 5069, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.452136", "y": "-34.601551"}, "direccion": "ESCALADA DE SAN MARTIN, R. 577, CABA", "nombre_calle": "ESCALADA DE SAN MARTIN, R.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>-58.373937</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-34.601335</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>S00164926</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NAON ROMULO 2381</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 2381, "cod_calle": 6040, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.472548", "y": "-34.567521"}, "direccion": "NAON, ROMULO 2381, CABA", "nombre_calle": "NAON, ROMULO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>-58.472548</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-34.567521</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Colegiales</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>S00384650</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>4/11/2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MANZONI 106</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 106, "cod_calle": 13027, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.499154", "y": "-34.638825"}, "direccion": "MANZONI 106, CABA", "nombre_calle": "MANZONI", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>-58.499154</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-34.638825</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Devoto</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>Capital Norte</t>
         </is>

--- a/mapa_interactivo_Optical_Power.xlsx
+++ b/mapa_interactivo_Optical_Power.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,7 +507,11 @@
       <c r="D2" t="n">
         <v>12</v>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03732605 </t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>Optical Power</t>
@@ -559,7 +563,11 @@
       <c r="D3" t="n">
         <v>12</v>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03732939 </t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>Optical Power</t>
@@ -619,7 +627,11 @@
       <c r="D4" t="n">
         <v>12</v>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03733598 </t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Optical Power</t>
@@ -679,7 +691,11 @@
       <c r="D5" t="n">
         <v>2</v>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03730209 </t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>Optical Power</t>
@@ -739,7 +755,11 @@
       <c r="D6" t="n">
         <v>13</v>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03733730 </t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>Optical Power</t>
@@ -799,7 +819,11 @@
       <c r="D7" t="n">
         <v>13</v>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03733876 </t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>Optical Power</t>
@@ -859,7 +883,11 @@
       <c r="D8" t="n">
         <v>12</v>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03734392 </t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>Optical Power</t>
@@ -919,7 +947,11 @@
       <c r="D9" t="n">
         <v>1</v>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03730921 </t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>Optical Power</t>
@@ -979,7 +1011,11 @@
       <c r="D10" t="n">
         <v>13</v>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03734641 </t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>Optical Power</t>
@@ -1039,7 +1075,11 @@
       <c r="D11" t="n">
         <v>10</v>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03734759 </t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>Optical Power</t>
@@ -1075,6 +1115,262 @@
         </is>
       </c>
       <c r="N11" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>S00344962</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>4/14/2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ALBERDI, JUAN BAUTISTA AV. 3840</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>9</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>813113244</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 3840, "cod_calle": 1033, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.479124", "y": "-34.637357"}, "direccion": "ALBERDI, JUAN BAUTISTA AV. 3840, CABA", "nombre_calle": "ALBERDI, JUAN BAUTISTA AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>-58.479124</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-34.637357</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Devoto</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>S00384928</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>4/14/2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>LOPE DE VEGA 267</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>813113274</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 267, "cod_calle": 12126, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.499765", "y": "-34.635661"}, "direccion": "LOPE DE VEGA 267, CABA", "nombre_calle": "LOPE DE VEGA", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>-58.499765</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-34.635661</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Devoto</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>S00420728</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>4/14/2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ECUADOR 1394</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>813113291</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>NORMALIZAR CABLES FUERA DE NORMA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 1394, "cod_calle": 5001, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.403782", "y": "-34.594307"}, "direccion": "ECUADOR 1394, CABA", "nombre_calle": "ECUADOR", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>-58.403782</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-34.594307</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>M00002</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>4/17/2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MELIAN AV 3893</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>PEDIDA APP</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>DESPUES DE CORRIMIENTO DE COLUMNA NORMALIZAR NAP Y CDO.</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 3893, "cod_calle": 13063, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.481571", "y": "-34.552784"}, "direccion": "MELIAN AV. 3893, CABA", "nombre_calle": "MELIAN AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>-58.481571</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-34.552784</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>Capital Norte</t>
         </is>

--- a/mapa_interactivo_Optical_Power.xlsx
+++ b/mapa_interactivo_Optical_Power.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,25 +547,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00147974</t>
+          <t>S00363996</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3/21/2026</t>
+          <t>4/11/2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CAMINO MIGUEL ANDRES 3710</t>
+          <t>CONGRESO 2077</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03732939 </t>
+          <t xml:space="preserve">03733876 </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -580,7 +580,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>NORMALIZAR RED A BAJA ALTURA</t>
+          <t>CABLE SUELTO</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -588,18 +588,18 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 3710, "cod_calle": 3037, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.501857", "y": "-34.564503"}, "direccion": "CAMINO, MIGUEL ANDRÉS 3710, CABA", "nombre_calle": "CAMINO, MIGUEL ANDRÉS", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 2077, "cod_calle": 3156, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.459312", "y": "-34.553673"}, "direccion": "CONGRESO 2077, CABA", "nombre_calle": "CONGRESO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>-58.501857</v>
+        <v>-58.459312</v>
       </c>
       <c r="L3" t="n">
-        <v>-34.564503</v>
+        <v>-34.553673</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -611,25 +611,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00203594</t>
+          <t>S00160880</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3/28/2026</t>
+          <t>4/11/2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CRAMER 4061</t>
+          <t>SAN MARTIN 577</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">03733598 </t>
+          <t xml:space="preserve">03730921 </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
+          <t>NORMALIZAR CABLES CON MEDIA CAÑA EN FACHADA</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -652,48 +652,48 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 4061, "cod_calle": 3189, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.475268", "y": "-34.547194"}, "direccion": "CRAMER 4061, CABA", "nombre_calle": "CRAMER", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 577, "cod_calle": 20044, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.373937", "y": "-34.601335"}, "direccion": "SAN MARTIN 577, CABA", "nombre_calle": "SAN MARTIN", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}, {"altura": 577, "cod_calle": 5069, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.452136", "y": "-34.601551"}, "direccion": "ESCALADA DE SAN MARTIN, R. 577, CABA", "nombre_calle": "ESCALADA DE SAN MARTIN, R.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-58.475268</v>
+        <v>-58.373937</v>
       </c>
       <c r="L4" t="n">
-        <v>-34.547194</v>
+        <v>-34.601335</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S00328955</t>
+          <t>M00002</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4/11/2026</t>
+          <t>4/17/2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AV CALLAO 2014</t>
+          <t>MELIAN AV 3893</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">03730209 </t>
+          <t xml:space="preserve">03792376 </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -708,56 +708,56 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>NORMALIZAR CABLES CAIDOS</t>
+          <t>DESPUES DE CORRIMIENTO DE COLUMNA NORMALIZAR NAP Y CDO.</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 2014, "cod_calle": 3030, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.386954", "y": "-34.587337"}, "direccion": "CALLAO AV. 2014, CABA", "nombre_calle": "CALLAO AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 3893, "cod_calle": 13063, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.481571", "y": "-34.552784"}, "direccion": "MELIAN AV. 3893, CABA", "nombre_calle": "MELIAN AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>-58.386954</v>
+        <v>-58.481571</v>
       </c>
       <c r="L5" t="n">
-        <v>-34.587337</v>
+        <v>-34.552784</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S00328057</t>
+          <t>8116</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4/11/2026</t>
+          <t>4/20/2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OHIGGINS 2328</t>
+          <t>MEXICO 2553</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">03733730 </t>
+          <t>APP P.ADMIN</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>NORMALIZAR CABLES CAIDOS</t>
+          <t>NORMALIZAR CABLES EN DESUSO</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -780,48 +780,48 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 2328, "cod_calle": 16009, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.454826", "y": "-34.557740"}, "direccion": "O'HIGGINS 2328, CABA", "nombre_calle": "O'HIGGINS", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 2553, "cod_calle": 13076, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.401935", "y": "-34.616604"}, "direccion": "MEXICO 2553, CABA", "nombre_calle": "MEXICO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-58.454826</v>
+        <v>-58.401935</v>
       </c>
       <c r="L6" t="n">
-        <v>-34.55774</v>
+        <v>-34.616604</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S00363996</t>
+          <t>S00392154</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4/11/2026</t>
+          <t>4/20/2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CONGRESO 2077</t>
+          <t>MOLDES 3802</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">03733876 </t>
+          <t>APP.P ADMIN</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>CABLE SUELTO</t>
+          <t>NORMALIZAR CABLES FUERA DE NORMA</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -844,14 +844,14 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 2077, "cod_calle": 3156, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.459312", "y": "-34.553673"}, "direccion": "CONGRESO 2077, CABA", "nombre_calle": "CONGRESO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 3802, "cod_calle": 13099, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.472225", "y": "-34.548862"}, "direccion": "MOLDES 3802, CABA", "nombre_calle": "MOLDES", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-58.459312</v>
+        <v>-58.472225</v>
       </c>
       <c r="L7" t="n">
-        <v>-34.553673</v>
+        <v>-34.548862</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -867,17 +867,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8876</t>
+          <t>S00410561</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4/11/2026</t>
+          <t>4/20/2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PICO 1597</t>
+          <t>ANDONAEGUI 1824</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -885,7 +885,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">03734392 </t>
+          <t>APP.P ADMIN</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
+          <t>NORMALIZAR CABLES SOBRE LA FACHADA</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -908,18 +908,18 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 1597, "cod_calle": 17074, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.466221", "y": "-34.536587"}, "direccion": "PICO 1597, CABA", "nombre_calle": "PICO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 1824, "cod_calle": 1082, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.484495", "y": "-34.581735"}, "direccion": "ANDONAEGUI 1824, CABA", "nombre_calle": "ANDONAEGUI", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-58.466221</v>
+        <v>-58.484495</v>
       </c>
       <c r="L8" t="n">
-        <v>-34.536587</v>
+        <v>-34.581735</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -931,25 +931,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S00160880</t>
+          <t>S00415175</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4/11/2026</t>
+          <t>4/20/2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SAN MARTIN 577</t>
+          <t>ARANGUREN, JUAN F., DR. 4894</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">03730921 </t>
+          <t>APP.P ADMIN</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>NORMALIZAR CABLES CON MEDIA CAÑA EN FACHADA</t>
+          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -972,48 +972,48 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 577, "cod_calle": 20044, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.373937", "y": "-34.601335"}, "direccion": "SAN MARTIN 577, CABA", "nombre_calle": "SAN MARTIN", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}, {"altura": 577, "cod_calle": 5069, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.452136", "y": "-34.601551"}, "direccion": "ESCALADA DE SAN MARTIN, R. 577, CABA", "nombre_calle": "ESCALADA DE SAN MARTIN, R.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 4894, "cod_calle": 1094, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.495815", "y": "-34.632491"}, "direccion": "ARANGUREN, JUAN F., DR. 4894, CABA", "nombre_calle": "ARANGUREN, JUAN F., DR.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-58.373937</v>
+        <v>-58.495815</v>
       </c>
       <c r="L9" t="n">
-        <v>-34.601335</v>
+        <v>-34.632491</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S00164926</t>
+          <t>S00445810</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4/11/2026</t>
+          <t>4/21/2026</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NAON ROMULO 2381</t>
+          <t>VIRGILIO 428</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">03734641 </t>
+          <t>APP.P ADMIN</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1036,18 +1036,18 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 2381, "cod_calle": 6040, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.472548", "y": "-34.567521"}, "direccion": "NAON, ROMULO 2381, CABA", "nombre_calle": "NAON, ROMULO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 428, "cod_calle": 23073, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.501742", "y": "-34.633742"}, "direccion": "VIRGILIO 428, CABA", "nombre_calle": "VIRGILIO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-58.472548</v>
+        <v>-58.501742</v>
       </c>
       <c r="L10" t="n">
-        <v>-34.567521</v>
+        <v>-34.633742</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1059,25 +1059,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S00384650</t>
+          <t>S00368133</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4/11/2026</t>
+          <t>4/21/2026</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MANZONI 106</t>
+          <t>BOCAYUVA, QUINTINO 1059</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">03734759 </t>
+          <t>APP.P ADMIN</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
+          <t>NORMALIZAR CABLES A BAJA ALTURA SACAR CABLES QUE PASAN DENTRO DEL ARBOL</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1100,48 +1100,48 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 106, "cod_calle": 13027, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.499154", "y": "-34.638825"}, "direccion": "MANZONI 106, CABA", "nombre_calle": "MANZONI", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 1059, "cod_calle": 2086, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.421740", "y": "-34.625564"}, "direccion": "BOCAYUVA, QUINTINO 1059, CABA", "nombre_calle": "BOCAYUVA, QUINTINO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>-58.499154</v>
+        <v>-58.42174</v>
       </c>
       <c r="L11" t="n">
-        <v>-34.638825</v>
+        <v>-34.625564</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S00344962</t>
+          <t>S00443411</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4/14/2026</t>
+          <t>4/21/2026</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 3840</t>
+          <t>CERVANTES 1139</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>813113244</t>
+          <t>APP.P ADMIN</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1164,14 +1164,14 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 3840, "cod_calle": 1033, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.479124", "y": "-34.637357"}, "direccion": "ALBERDI, JUAN BAUTISTA AV. 3840, CABA", "nombre_calle": "ALBERDI, JUAN BAUTISTA AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 1139, "cod_calle": 3119, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.501159", "y": "-34.627924"}, "direccion": "CERVANTES 1139, CABA", "nombre_calle": "CERVANTES", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-58.479124</v>
+        <v>-58.501159</v>
       </c>
       <c r="L12" t="n">
-        <v>-34.637357</v>
+        <v>-34.627924</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1179,198 +1179,6 @@
         </is>
       </c>
       <c r="N12" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>S00384928</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>4/14/2026</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>LOPE DE VEGA 267</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>813113274</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>{"direccionesNormalizadas": [{"altura": 267, "cod_calle": 12126, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.499765", "y": "-34.635661"}, "direccion": "LOPE DE VEGA 267, CABA", "nombre_calle": "LOPE DE VEGA", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>-58.499765</v>
-      </c>
-      <c r="L13" t="n">
-        <v>-34.635661</v>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Devoto</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>S00420728</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>4/14/2026</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>ECUADOR 1394</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>813113291</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>NORMALIZAR CABLES FUERA DE NORMA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>{"direccionesNormalizadas": [{"altura": 1394, "cod_calle": 5001, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.403782", "y": "-34.594307"}, "direccion": "ECUADOR 1394, CABA", "nombre_calle": "ECUADOR", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>-58.403782</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-34.594307</v>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Recoleta</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>M00002</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>4/17/2026</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>MELIAN AV 3893</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>12</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>PEDIDA APP</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>DESPUES DE CORRIMIENTO DE COLUMNA NORMALIZAR NAP Y CDO.</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>{"direccionesNormalizadas": [{"altura": 3893, "cod_calle": 13063, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.481571", "y": "-34.552784"}, "direccion": "MELIAN AV. 3893, CABA", "nombre_calle": "MELIAN AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>-58.481571</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-34.552784</v>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Saavedra</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
         <is>
           <t>Capital Norte</t>
         </is>

--- a/mapa_interactivo_Optical_Power.xlsx
+++ b/mapa_interactivo_Optical_Power.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -611,25 +611,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S00160880</t>
+          <t>M00002</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4/11/2026</t>
+          <t>4/17/2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SAN MARTIN 577</t>
+          <t>MELIAN AV 3893</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">03730921 </t>
+          <t xml:space="preserve">03792376 </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -644,48 +644,48 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NORMALIZAR CABLES CON MEDIA CAÑA EN FACHADA</t>
+          <t>DESPUES DE CORRIMIENTO DE COLUMNA NORMALIZAR NAP Y CDO.</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 577, "cod_calle": 20044, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.373937", "y": "-34.601335"}, "direccion": "SAN MARTIN 577, CABA", "nombre_calle": "SAN MARTIN", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}, {"altura": 577, "cod_calle": 5069, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.452136", "y": "-34.601551"}, "direccion": "ESCALADA DE SAN MARTIN, R. 577, CABA", "nombre_calle": "ESCALADA DE SAN MARTIN, R.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 3893, "cod_calle": 13063, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.481571", "y": "-34.552784"}, "direccion": "MELIAN AV. 3893, CABA", "nombre_calle": "MELIAN AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-58.373937</v>
+        <v>-58.481571</v>
       </c>
       <c r="L4" t="n">
-        <v>-34.601335</v>
+        <v>-34.552784</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M00002</t>
+          <t>S00392154</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4/17/2026</t>
+          <t>4/20/2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MELIAN AV 3893</t>
+          <t>MOLDES 3802</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -693,7 +693,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">03792376 </t>
+          <t>APP.P ADMIN</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DESPUES DE CORRIMIENTO DE COLUMNA NORMALIZAR NAP Y CDO.</t>
+          <t>NORMALIZAR CABLES FUERA DE NORMA</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 3893, "cod_calle": 13063, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.481571", "y": "-34.552784"}, "direccion": "MELIAN AV. 3893, CABA", "nombre_calle": "MELIAN AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 3802, "cod_calle": 13099, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.472225", "y": "-34.548862"}, "direccion": "MOLDES 3802, CABA", "nombre_calle": "MOLDES", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>-58.481571</v>
+        <v>-58.472225</v>
       </c>
       <c r="L5" t="n">
-        <v>-34.552784</v>
+        <v>-34.548862</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8116</t>
+          <t>S00410561</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -749,15 +749,15 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MEXICO 2553</t>
+          <t>ANDONAEGUI 1824</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>APP P.ADMIN</t>
+          <t>APP.P ADMIN</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>NORMALIZAR CABLES EN DESUSO</t>
+          <t>NORMALIZAR CABLES SOBRE LA FACHADA</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -780,30 +780,30 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 2553, "cod_calle": 13076, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.401935", "y": "-34.616604"}, "direccion": "MEXICO 2553, CABA", "nombre_calle": "MEXICO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 1824, "cod_calle": 1082, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.484495", "y": "-34.581735"}, "direccion": "ANDONAEGUI 1824, CABA", "nombre_calle": "ANDONAEGUI", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-58.401935</v>
+        <v>-58.484495</v>
       </c>
       <c r="L6" t="n">
-        <v>-34.616604</v>
+        <v>-34.581735</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S00392154</t>
+          <t>S00415175</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -813,11 +813,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MOLDES 3802</t>
+          <t>ARANGUREN, JUAN F., DR. 4894</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>NORMALIZAR CABLES FUERA DE NORMA</t>
+          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -844,18 +844,18 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 3802, "cod_calle": 13099, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.472225", "y": "-34.548862"}, "direccion": "MOLDES 3802, CABA", "nombre_calle": "MOLDES", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 4894, "cod_calle": 1094, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.495815", "y": "-34.632491"}, "direccion": "ARANGUREN, JUAN F., DR. 4894, CABA", "nombre_calle": "ARANGUREN, JUAN F., DR.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-58.472225</v>
+        <v>-58.495815</v>
       </c>
       <c r="L7" t="n">
-        <v>-34.548862</v>
+        <v>-34.632491</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -867,27 +867,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S00410561</t>
+          <t>S01221719</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4/20/2026</t>
+          <t>4/21/2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ANDONAEGUI 1824</t>
+          <t>NEUQUEN 2140</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>APP.P ADMIN</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>Optical Power</t>
@@ -900,7 +896,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NORMALIZAR CABLES SOBRE LA FACHADA</t>
+          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -908,50 +904,46 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 1824, "cod_calle": 1082, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.484495", "y": "-34.581735"}, "direccion": "ANDONAEGUI 1824, CABA", "nombre_calle": "ANDONAEGUI", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 2140, "cod_calle": 14017, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.462870", "y": "-34.617270"}, "direccion": "NEUQUEN 2140, CABA", "nombre_calle": "NEUQUEN", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-58.484495</v>
+        <v>-58.46287</v>
       </c>
       <c r="L8" t="n">
-        <v>-34.581735</v>
+        <v>-34.61727</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S00415175</t>
+          <t>S01230406</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4/20/2026</t>
+          <t>4/21/2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ARANGUREN, JUAN F., DR. 4894</t>
+          <t>GOYENA, PEDRO AV. 1763</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>APP.P ADMIN</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>Optical Power</t>
@@ -972,30 +964,30 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 4894, "cod_calle": 1094, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.495815", "y": "-34.632491"}, "direccion": "ARANGUREN, JUAN F., DR. 4894, CABA", "nombre_calle": "ARANGUREN, JUAN F., DR.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 1763, "cod_calle": 7074, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.453478", "y": "-34.628656"}, "direccion": "GOYENA, PEDRO AV. 1763, CABA", "nombre_calle": "GOYENA, PEDRO AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-58.495815</v>
+        <v>-58.453478</v>
       </c>
       <c r="L9" t="n">
-        <v>-34.632491</v>
+        <v>-34.628656</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S00445810</t>
+          <t>S01307009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1005,17 +997,13 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>VIRGILIO 428</t>
+          <t>TANDIL 3901</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>APP.P ADMIN</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>Optical Power</t>
@@ -1036,14 +1024,14 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 428, "cod_calle": 23073, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.501742", "y": "-34.633742"}, "direccion": "VIRGILIO 428, CABA", "nombre_calle": "VIRGILIO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 3901, "cod_calle": 21011, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.478305", "y": "-34.641004"}, "direccion": "TANDIL 3901, CABA", "nombre_calle": "TANDIL", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-58.501742</v>
+        <v>-58.478305</v>
       </c>
       <c r="L10" t="n">
-        <v>-34.633742</v>
+        <v>-34.641004</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1059,7 +1047,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S00368133</t>
+          <t>S01314513</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1069,17 +1057,13 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BOCAYUVA, QUINTINO 1059</t>
+          <t>CARABOBO AV. 581</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>APP.P ADMIN</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>Optical Power</t>
@@ -1092,7 +1076,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>NORMALIZAR CABLES A BAJA ALTURA SACAR CABLES QUE PASAN DENTRO DEL ARBOL</t>
+          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1100,14 +1084,14 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 1059, "cod_calle": 2086, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.421740", "y": "-34.625564"}, "direccion": "BOCAYUVA, QUINTINO 1059, CABA", "nombre_calle": "BOCAYUVA, QUINTINO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 581, "cod_calle": 3061, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.453626", "y": "-34.633260"}, "direccion": "CARABOBO AV. 581, CABA", "nombre_calle": "CARABOBO AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>-58.42174</v>
+        <v>-58.453626</v>
       </c>
       <c r="L11" t="n">
-        <v>-34.625564</v>
+        <v>-34.63326</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1123,27 +1107,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S00443411</t>
+          <t>9032</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4/21/2026</t>
+          <t>4/24/2026</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CERVANTES 1139</t>
+          <t>CERETTI 2089</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>APP.P ADMIN</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>Optical Power</t>
@@ -1156,7 +1136,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
+          <t>NORMALIZAR CABLES BAJOS</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1164,23 +1144,83 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 1139, "cod_calle": 3119, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.501159", "y": "-34.627924"}, "direccion": "CERVANTES 1139, CABA", "nombre_calle": "CERVANTES", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 2089, "cod_calle": 3115, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.490439", "y": "-34.581351"}, "direccion": "CERETTI 2089, CABA", "nombre_calle": "CERETTI", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-58.501159</v>
+        <v>-58.490439</v>
       </c>
       <c r="L12" t="n">
-        <v>-34.627924</v>
+        <v>-34.581351</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>Capital Norte</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>S00421935</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>4/24/2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA AV. 741</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 741, "cod_calle": 9010, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.376567", "y": "-34.617309"}, "direccion": "INDEPENDENCIA AV. 741, CABA", "nombre_calle": "INDEPENDENCIA AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>-58.376567</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-34.617309</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
         </is>
       </c>
     </row>

--- a/mapa_interactivo_Optical_Power.xlsx
+++ b/mapa_interactivo_Optical_Power.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,25 +547,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S00363996</t>
+          <t>M00002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4/11/2026</t>
+          <t>4/17/2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CONGRESO 2077</t>
+          <t>MELIAN AV 3893</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03733876 </t>
+          <t xml:space="preserve">03792376 </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -580,22 +580,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CABLE SUELTO</t>
+          <t>DESPUES DE CORRIMIENTO DE COLUMNA NORMALIZAR NAP Y CDO.</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 2077, "cod_calle": 3156, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.459312", "y": "-34.553673"}, "direccion": "CONGRESO 2077, CABA", "nombre_calle": "CONGRESO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 3893, "cod_calle": 13063, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.481571", "y": "-34.552784"}, "direccion": "MELIAN AV. 3893, CABA", "nombre_calle": "MELIAN AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>-58.459312</v>
+        <v>-58.481571</v>
       </c>
       <c r="L3" t="n">
-        <v>-34.553673</v>
+        <v>-34.552784</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -611,17 +611,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M00002</t>
+          <t>S00392154</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4/17/2026</t>
+          <t>4/20/2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MELIAN AV 3893</t>
+          <t>MOLDES 3802</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -629,7 +629,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">03792376 </t>
+          <t xml:space="preserve">03863625 </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -644,22 +644,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DESPUES DE CORRIMIENTO DE COLUMNA NORMALIZAR NAP Y CDO.</t>
+          <t>NORMALIZAR CABLES FUERA DE NORMA</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 3893, "cod_calle": 13063, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.481571", "y": "-34.552784"}, "direccion": "MELIAN AV. 3893, CABA", "nombre_calle": "MELIAN AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 3802, "cod_calle": 13099, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.472225", "y": "-34.548862"}, "direccion": "MOLDES 3802, CABA", "nombre_calle": "MOLDES", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-58.481571</v>
+        <v>-58.472225</v>
       </c>
       <c r="L4" t="n">
-        <v>-34.552784</v>
+        <v>-34.548862</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S00392154</t>
+          <t>S00410561</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MOLDES 3802</t>
+          <t>ANDONAEGUI 1824</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -693,7 +693,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>APP.P ADMIN</t>
+          <t xml:space="preserve">03863944 </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>NORMALIZAR CABLES FUERA DE NORMA</t>
+          <t>NORMALIZAR CABLES SOBRE LA FACHADA</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -716,18 +716,18 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 3802, "cod_calle": 13099, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.472225", "y": "-34.548862"}, "direccion": "MOLDES 3802, CABA", "nombre_calle": "MOLDES", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 1824, "cod_calle": 1082, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.484495", "y": "-34.581735"}, "direccion": "ANDONAEGUI 1824, CABA", "nombre_calle": "ANDONAEGUI", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>-58.472225</v>
+        <v>-58.484495</v>
       </c>
       <c r="L5" t="n">
-        <v>-34.548862</v>
+        <v>-34.581735</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S00410561</t>
+          <t>S00415175</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -749,15 +749,15 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ANDONAEGUI 1824</t>
+          <t>ARANGUREN, JUAN F., DR. 4894</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>APP.P ADMIN</t>
+          <t xml:space="preserve">03864108 </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>NORMALIZAR CABLES SOBRE LA FACHADA</t>
+          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -780,18 +780,18 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 1824, "cod_calle": 1082, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.484495", "y": "-34.581735"}, "direccion": "ANDONAEGUI 1824, CABA", "nombre_calle": "ANDONAEGUI", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 4894, "cod_calle": 1094, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.495815", "y": "-34.632491"}, "direccion": "ARANGUREN, JUAN F., DR. 4894, CABA", "nombre_calle": "ARANGUREN, JUAN F., DR.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-58.484495</v>
+        <v>-58.495815</v>
       </c>
       <c r="L6" t="n">
-        <v>-34.581735</v>
+        <v>-34.632491</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -803,25 +803,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S00415175</t>
+          <t>9032</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4/20/2026</t>
+          <t>4/24/2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARANGUREN, JUAN F., DR. 4894</t>
+          <t>CERETTI 2089</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>APP.P ADMIN</t>
+          <t>SE GENERA OT POR PEX</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
+          <t>NORMALIZAR CABLES BAJOS</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -844,18 +844,18 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 4894, "cod_calle": 1094, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.495815", "y": "-34.632491"}, "direccion": "ARANGUREN, JUAN F., DR. 4894, CABA", "nombre_calle": "ARANGUREN, JUAN F., DR.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 2089, "cod_calle": 3115, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.490439", "y": "-34.581351"}, "direccion": "CERETTI 2089, CABA", "nombre_calle": "CERETTI", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-58.495815</v>
+        <v>-58.490439</v>
       </c>
       <c r="L7" t="n">
-        <v>-34.632491</v>
+        <v>-34.581351</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -867,23 +867,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S01221719</t>
+          <t>S00421935</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4/21/2026</t>
+          <t>4/24/2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NEUQUEN 2140</t>
+          <t>INDEPENDENCIA AV. 741</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SE GENERA OT POR PEX</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>Optical Power</t>
@@ -904,18 +908,18 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 2140, "cod_calle": 14017, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.462870", "y": "-34.617270"}, "direccion": "NEUQUEN 2140, CABA", "nombre_calle": "NEUQUEN", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 741, "cod_calle": 9010, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.376567", "y": "-34.617309"}, "direccion": "INDEPENDENCIA AV. 741, CABA", "nombre_calle": "INDEPENDENCIA AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-58.46287</v>
+        <v>-58.376567</v>
       </c>
       <c r="L8" t="n">
-        <v>-34.61727</v>
+        <v>-34.617309</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -927,23 +931,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S01230406</t>
+          <t>S00472155</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4/21/2026</t>
+          <t>4/29/2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GOYENA, PEDRO AV. 1763</t>
+          <t>MARTI, JOSE 3124</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>SE GENERA OT POR PEX</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>Optical Power</t>
@@ -964,261 +972,21 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 1763, "cod_calle": 7074, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.453478", "y": "-34.628656"}, "direccion": "GOYENA, PEDRO AV. 1763, CABA", "nombre_calle": "GOYENA, PEDRO AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 3124, "cod_calle": 13034, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.442102", "y": "-34.661270"}, "direccion": "MARTI, JOSE 3124, CABA", "nombre_calle": "MARTI, JOSE", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-58.453478</v>
+        <v>-58.442102</v>
       </c>
       <c r="L9" t="n">
-        <v>-34.628656</v>
+        <v>-34.66127</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>S01307009</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>4/21/2026</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>TANDIL 3901</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>9</v>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>{"direccionesNormalizadas": [{"altura": 3901, "cod_calle": 21011, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.478305", "y": "-34.641004"}, "direccion": "TANDIL 3901, CABA", "nombre_calle": "TANDIL", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>-58.478305</v>
-      </c>
-      <c r="L10" t="n">
-        <v>-34.641004</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Devoto</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>S01314513</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>4/21/2026</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>CARABOBO AV. 581</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>7</v>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>{"direccionesNormalizadas": [{"altura": 581, "cod_calle": 3061, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.453626", "y": "-34.633260"}, "direccion": "CARABOBO AV. 581, CABA", "nombre_calle": "CARABOBO AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>-58.453626</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-34.63326</v>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>9032</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>4/24/2026</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>CERETTI 2089</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>12</v>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>NORMALIZAR CABLES BAJOS</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>{"direccionesNormalizadas": [{"altura": 2089, "cod_calle": 3115, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.490439", "y": "-34.581351"}, "direccion": "CERETTI 2089, CABA", "nombre_calle": "CERETTI", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>-58.490439</v>
-      </c>
-      <c r="L12" t="n">
-        <v>-34.581351</v>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Paternal</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>S00421935</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>4/24/2026</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA AV. 741</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>3</v>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>{"direccionesNormalizadas": [{"altura": 741, "cod_calle": 9010, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.376567", "y": "-34.617309"}, "direccion": "INDEPENDENCIA AV. 741, CABA", "nombre_calle": "INDEPENDENCIA AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>-58.376567</v>
-      </c>
-      <c r="L13" t="n">
-        <v>-34.617309</v>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>San Telmo</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
         <is>
           <t>Capital Sur</t>
         </is>

--- a/mapa_interactivo_Optical_Power.xlsx
+++ b/mapa_interactivo_Optical_Power.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -611,25 +611,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S00392154</t>
+          <t>S00472155</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4/20/2026</t>
+          <t>4/29/2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MOLDES 3802</t>
+          <t>MARTI, JOSE 3124</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">03863625 </t>
+          <t xml:space="preserve">04033967 </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NORMALIZAR CABLES FUERA DE NORMA</t>
+          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -652,48 +652,48 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 3802, "cod_calle": 13099, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.472225", "y": "-34.548862"}, "direccion": "MOLDES 3802, CABA", "nombre_calle": "MOLDES", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 3124, "cod_calle": 13034, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.442102", "y": "-34.661270"}, "direccion": "MARTI, JOSE 3124, CABA", "nombre_calle": "MARTI, JOSE", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-58.472225</v>
+        <v>-58.442102</v>
       </c>
       <c r="L4" t="n">
-        <v>-34.548862</v>
+        <v>-34.66127</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S00410561</t>
+          <t>9073</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4/20/2026</t>
+          <t>4/30/2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ANDONAEGUI 1824</t>
+          <t>EL SALVADOR 5897</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">03863944 </t>
+          <t>PENDIENTE ADMIN</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>NORMALIZAR CABLES SOBRE LA FACHADA</t>
+          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -716,48 +716,48 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 1824, "cod_calle": 1082, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.484495", "y": "-34.581735"}, "direccion": "ANDONAEGUI 1824, CABA", "nombre_calle": "ANDONAEGUI", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 5897, "cod_calle": 5050, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.438216", "y": "-34.580964"}, "direccion": "EL SALVADOR 5897, CABA", "nombre_calle": "EL SALVADOR", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>-58.484495</v>
+        <v>-58.438216</v>
       </c>
       <c r="L5" t="n">
-        <v>-34.581735</v>
+        <v>-34.580964</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S00415175</t>
+          <t>9094</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4/20/2026</t>
+          <t>5/10/2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARANGUREN, JUAN F., DR. 4894</t>
+          <t>CARRIL, SALVADOR MARIA DEL AV. 3236</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">03864108 </t>
+          <t>PENDIENTE ADMIN</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -780,18 +780,18 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 4894, "cod_calle": 1094, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.495815", "y": "-34.632491"}, "direccion": "ARANGUREN, JUAN F., DR. 4894, CABA", "nombre_calle": "ARANGUREN, JUAN F., DR.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 3236, "cod_calle": 4039, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.502582", "y": "-34.593476"}, "direccion": "CARRIL, SALVADOR MARIA DEL AV. 3236, CABA", "nombre_calle": "CARRIL, SALVADOR MARIA DEL AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-58.495815</v>
+        <v>-58.502582</v>
       </c>
       <c r="L6" t="n">
-        <v>-34.632491</v>
+        <v>-34.593476</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -803,17 +803,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9032</t>
+          <t>9128</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>5/10/2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CERETTI 2089</t>
+          <t>ECHEVERRIA 5596</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -821,7 +821,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SE GENERA OT POR PEX</t>
+          <t>PENDIENTE ADMIN</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>NORMALIZAR CABLES BAJOS</t>
+          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -844,14 +844,14 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 2089, "cod_calle": 3115, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.490439", "y": "-34.581351"}, "direccion": "CERETTI 2089, CABA", "nombre_calle": "CERETTI", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 5596, "cod_calle": 5007, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.486598", "y": "-34.582134"}, "direccion": "ECHEVERRIA 5596, CABA", "nombre_calle": "ECHEVERRIA", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-58.490439</v>
+        <v>-58.486598</v>
       </c>
       <c r="L7" t="n">
-        <v>-34.581351</v>
+        <v>-34.582134</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -867,25 +867,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S00421935</t>
+          <t xml:space="preserve">9141 </t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA AV. 741</t>
+          <t>CUBAS, JOSE 4440</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SE GENERA OT POR PEX</t>
+          <t>PENDIENTE ADMIN</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
+          <t>DESMONTAR CABLES CORTADOS Y DESMONTAR POSTE INCLINADO</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -908,48 +908,48 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 741, "cod_calle": 9010, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.376567", "y": "-34.617309"}, "direccion": "INDEPENDENCIA AV. 741, CABA", "nombre_calle": "INDEPENDENCIA AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 4440, "cod_calle": 3198, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.519391", "y": "-34.600472"}, "direccion": "CUBAS, JOSE 4440, CABA", "nombre_calle": "CUBAS, JOSE", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-58.376567</v>
+        <v>-58.519391</v>
       </c>
       <c r="L8" t="n">
-        <v>-34.617309</v>
+        <v>-34.600472</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S00472155</t>
+          <t>S00347551</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4/29/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MARTI, JOSE 3124</t>
+          <t>BILBAO, FRANCISCO 2124</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SE GENERA OT POR PEX</t>
+          <t>PENDIENTE ADMIN</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -972,21 +972,1109 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 3124, "cod_calle": 13034, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.442102", "y": "-34.661270"}, "direccion": "MARTI, JOSE 3124, CABA", "nombre_calle": "MARTI, JOSE", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 2124, "cod_calle": 2081, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.456407", "y": "-34.633376"}, "direccion": "BILBAO, FRANCISCO 2124, CABA", "nombre_calle": "BILBAO, FRANCISCO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-58.442102</v>
+        <v>-58.456407</v>
       </c>
       <c r="L9" t="n">
-        <v>-34.66127</v>
+        <v>-34.633376</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>S00415298</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>5/13/2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CARDOSO 17</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>PENDIENTE ADMIN</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>NORMALIZAR TENDIDO A BAJA ALTURA</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 17, "cod_calle": 3070, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.492138", "y": "-34.635993"}, "direccion": "CARDOSO 17, CABA", "nombre_calle": "CARDOSO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>-58.492138</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-34.635993</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Devoto</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>S00435575</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>5/13/2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>LAMAS, ANDRES 1720</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>PENDIENTE ADMIN</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 1720, "cod_calle": 12040, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.467729", "y": "-34.609182"}, "direccion": "LAMAS, ANDRES 1720, CABA", "nombre_calle": "LAMAS, ANDRES", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>-58.467729</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-34.609182</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>S00456441</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5/13/2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>QUESADA 4154</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>PENDIENTE ADMIN</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>CORTAR CABLES EN DESUSO Y VERIFICAR ESTADO COLUMNA, DOCUMENTAR CON FOTOS</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 4154, "cod_calle": 18005, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.481018", "y": "-34.563694"}, "direccion": "QUESADA 4154, CABA", "nombre_calle": "QUESADA", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>-58.481018</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-34.563694</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9153 </t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>5/14/2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ALVAREZ THOMAS AV. 1720</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>15</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>PENDIENTE ADMIN</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 1720, "cod_calle": 1059, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.466347", "y": "-34.579162"}, "direccion": "ALVAREZ THOMAS AV. 1720, CABA", "nombre_calle": "ALVAREZ THOMAS AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>-58.466347</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-34.579162</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Colegiales</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9158 </t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>5/13/2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>FRANCO 2415</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>15</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>PENDIENTE ADMIN</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>MORMALIZAR TENDIDO A BAJA ALTURA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 2415, "cod_calle": 6052, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.501083", "y": "-34.578059"}, "direccion": "FRANCO 2415, CABA", "nombre_calle": "FRANCO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>-58.501083</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-34.578059</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9159 </t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>5/13/2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BAZURCO 2442</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>PENDIENTE ADMIN</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>NORMALIZAR TENDIDO A BAJA ALTURA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 2442, "cod_calle": 2038, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.502043", "y": "-34.577603"}, "direccion": "BAZURCO 2442, CABA", "nombre_calle": "BAZURCO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>-58.502043</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-34.577603</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>9160</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>5/13/2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CARACAS 5377</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>PENDIENTE ADMIN</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>NORMALIZAR RED A BAJA ALTURA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 5377, "cod_calle": 3062, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.500199", "y": "-34.576706"}, "direccion": "CARACAS 5377, CABA", "nombre_calle": "CARACAS", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>-58.500199</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-34.576706</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9185 </t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>5/13/2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CAMARGO 1157</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>15</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>PENDIENTE ADMIN</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>NORMALIZAR RED A BAJA ALTURA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 1157, "cod_calle": 3033, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.445853", "y": "-34.595224"}, "direccion": "CAMARGO 1157, CABA", "nombre_calle": "CAMARGO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>-58.445853</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-34.595224</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9188 </t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5/13/2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BARZANA 1566</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>PENDIENTE ADMIN</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>NORMALIZAR RED A BAJA ALTURA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 1566, "cod_calle": 2023, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.483554", "y": "-34.584619"}, "direccion": "BARZANA 1566, CABA", "nombre_calle": "BARZANA", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>-58.483554</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-34.584619</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9190 </t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>5/13/2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>14 DE JULIO 1303</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>15</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>PENDIENTE ADMIN</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>NORMALIZAR RED A BAJA ALTURA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 1303, "cod_calle": 3102, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.461808", "y": "-34.578166"}, "direccion": "14 DE JULIO 1303, CABA", "nombre_calle": "14 DE JULIO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>-58.461808</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-34.578166</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Colegiales</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">900009976010 </t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>5/13/2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>JUNCAL 1887</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>PENDIENTE ADMIN</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 1887, "cod_calle": 10014, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.394228", "y": "-34.593596"}, "direccion": "JUNCAL 1887, CABA", "nombre_calle": "JUNCAL", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>-58.394228</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-34.593596</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9922 </t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>5/13/2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ESTADO DE PALESTINA 1014</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>PENDIENTE ADMIN</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 1014, "cod_calle": 19016, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.425117", "y": "-34.598984"}, "direccion": "ESTADO DE PALESTINA 1014, CABA", "nombre_calle": "ESTADO DE PALESTINA", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>-58.425117</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-34.598984</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9990 </t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>5/13/2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>COPAHUE 2065</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>4</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PENDIENTE ADMIN</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 2065, "cod_calle": 3162, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.379683", "y": "-34.641191"}, "direccion": "COPAHUE 2065, CABA", "nombre_calle": "COPAHUE", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>-58.379683</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-34.641191</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
           <t>San Telmo</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7789 </t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>5/14/2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>TAGLE 2640</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>14</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>PENDIENTE ADMIN</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 2640, "cod_calle": 21006, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.399601", "y": "-34.583071"}, "direccion": "TAGLE 2640, CABA", "nombre_calle": "TAGLE", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>-58.399601</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-34.583071</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7993 </t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>5/14/2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PUEYRREDON AV. 394</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>PENDIENTE ADMIN</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 394, "cod_calle": 17132, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.405850", "y": "-34.605697"}, "direccion": "PUEYRREDON AV. 394, CABA", "nombre_calle": "PUEYRREDON AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}, {"altura": 394, "cod_calle": 17133, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.440806", "y": "-34.615134"}, "direccion": "PUEYRREDON, HONORIO, DR. AV. 394, CABA", "nombre_calle": "PUEYRREDON, HONORIO, DR. AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>-58.40585</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-34.605697</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10051 </t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>5/14/2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>MOSCONI GENERAL AV. 2362</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>PENDIENTE ADMIN</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>NORMALIZAR CABLES EN DESUSO Y A BAJA ALTURA</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 2362, "cod_calle": 13135, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.495996", "y": "-34.582554"}, "direccion": "MOSCONI GENERAL AV. 2362, CABA", "nombre_calle": "MOSCONI GENERAL AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>-58.495996</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-34.582554</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10064 </t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>5/14/2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CORDOBA AV. 5187</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>14</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>PENDIENTE ADMIN</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>{"direccionesNormalizadas": [{"altura": 5187, "cod_calle": 3165, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.435882", "y": "-34.590339"}, "direccion": "CORDOBA AV. 5187, CABA", "nombre_calle": "CORDOBA AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>-58.435882</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-34.590339</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t>Capital Sur</t>
         </is>

--- a/mapa_interactivo_Optical_Power.xlsx
+++ b/mapa_interactivo_Optical_Power.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,21 +675,21 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9073</t>
+          <t>9094</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>5/10/2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>EL SALVADOR 5897</t>
+          <t>CARRIL, SALVADOR MARIA DEL AV. 3236</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -716,44 +716,44 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 5897, "cod_calle": 5050, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.438216", "y": "-34.580964"}, "direccion": "EL SALVADOR 5897, CABA", "nombre_calle": "EL SALVADOR", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 3236, "cod_calle": 4039, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.502582", "y": "-34.593476"}, "direccion": "CARRIL, SALVADOR MARIA DEL AV. 3236, CABA", "nombre_calle": "CARRIL, SALVADOR MARIA DEL AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>-58.438216</v>
+        <v>-58.502582</v>
       </c>
       <c r="L5" t="n">
-        <v>-34.580964</v>
+        <v>-34.593476</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9094</t>
+          <t>S00415298</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5/10/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CARRIL, SALVADOR MARIA DEL AV. 3236</t>
+          <t>CARDOSO 17</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
+          <t>NORMALIZAR TENDIDO A BAJA ALTURA</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -780,18 +780,18 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 3236, "cod_calle": 4039, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.502582", "y": "-34.593476"}, "direccion": "CARRIL, SALVADOR MARIA DEL AV. 3236, CABA", "nombre_calle": "CARRIL, SALVADOR MARIA DEL AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 17, "cod_calle": 3070, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.492138", "y": "-34.635993"}, "direccion": "CARDOSO 17, CABA", "nombre_calle": "CARDOSO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-58.502582</v>
+        <v>-58.492138</v>
       </c>
       <c r="L6" t="n">
-        <v>-34.593476</v>
+        <v>-34.635993</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -803,21 +803,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9128</t>
+          <t xml:space="preserve">9153 </t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5/10/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ECHEVERRIA 5596</t>
+          <t>ALVAREZ THOMAS AV. 1720</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -844,18 +844,18 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 5596, "cod_calle": 5007, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.486598", "y": "-34.582134"}, "direccion": "ECHEVERRIA 5596, CABA", "nombre_calle": "ECHEVERRIA", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 1720, "cod_calle": 1059, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.466347", "y": "-34.579162"}, "direccion": "ALVAREZ THOMAS AV. 1720, CABA", "nombre_calle": "ALVAREZ THOMAS AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-58.486598</v>
+        <v>-58.466347</v>
       </c>
       <c r="L7" t="n">
-        <v>-34.582134</v>
+        <v>-34.579162</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -867,7 +867,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">9141 </t>
+          <t xml:space="preserve">9158 </t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -877,11 +877,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CUBAS, JOSE 4440</t>
+          <t>FRANCO 2415</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DESMONTAR CABLES CORTADOS Y DESMONTAR POSTE INCLINADO</t>
+          <t>MORMALIZAR TENDIDO A BAJA ALTURA</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -908,14 +908,14 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 4440, "cod_calle": 3198, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.519391", "y": "-34.600472"}, "direccion": "CUBAS, JOSE 4440, CABA", "nombre_calle": "CUBAS, JOSE", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 2415, "cod_calle": 6052, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.501083", "y": "-34.578059"}, "direccion": "FRANCO 2415, CABA", "nombre_calle": "FRANCO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-58.519391</v>
+        <v>-58.501083</v>
       </c>
       <c r="L8" t="n">
-        <v>-34.600472</v>
+        <v>-34.578059</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S00347551</t>
+          <t xml:space="preserve">9159 </t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -941,11 +941,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BILBAO, FRANCISCO 2124</t>
+          <t>BAZURCO 2442</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
+          <t>NORMALIZAR TENDIDO A BAJA ALTURA</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -972,30 +972,30 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 2124, "cod_calle": 2081, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.456407", "y": "-34.633376"}, "direccion": "BILBAO, FRANCISCO 2124, CABA", "nombre_calle": "BILBAO, FRANCISCO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 2442, "cod_calle": 2038, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.502043", "y": "-34.577603"}, "direccion": "BAZURCO 2442, CABA", "nombre_calle": "BAZURCO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-58.456407</v>
+        <v>-58.502043</v>
       </c>
       <c r="L9" t="n">
-        <v>-34.633376</v>
+        <v>-34.577603</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S00415298</t>
+          <t>9160</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1005,11 +1005,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CARDOSO 17</t>
+          <t>CARACAS 5377</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>NORMALIZAR TENDIDO A BAJA ALTURA</t>
+          <t>NORMALIZAR RED A BAJA ALTURA</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -1036,18 +1036,18 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 17, "cod_calle": 3070, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.492138", "y": "-34.635993"}, "direccion": "CARDOSO 17, CABA", "nombre_calle": "CARDOSO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 5377, "cod_calle": 3062, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.500199", "y": "-34.576706"}, "direccion": "CARACAS 5377, CABA", "nombre_calle": "CARACAS", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-58.492138</v>
+        <v>-58.500199</v>
       </c>
       <c r="L10" t="n">
-        <v>-34.635993</v>
+        <v>-34.576706</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1059,7 +1059,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S00435575</t>
+          <t xml:space="preserve">9185 </t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1069,11 +1069,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LAMAS, ANDRES 1720</t>
+          <t>CAMARGO 1157</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
+          <t>NORMALIZAR RED A BAJA ALTURA</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1100,14 +1100,14 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 1720, "cod_calle": 12040, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.467729", "y": "-34.609182"}, "direccion": "LAMAS, ANDRES 1720, CABA", "nombre_calle": "LAMAS, ANDRES", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 1157, "cod_calle": 3033, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.445853", "y": "-34.595224"}, "direccion": "CAMARGO 1157, CABA", "nombre_calle": "CAMARGO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>-58.467729</v>
+        <v>-58.445853</v>
       </c>
       <c r="L11" t="n">
-        <v>-34.609182</v>
+        <v>-34.595224</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S00456441</t>
+          <t xml:space="preserve">900009976010 </t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1133,11 +1133,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>QUESADA 4154</t>
+          <t>JUNCAL 1887</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CORTAR CABLES EN DESUSO Y VERIFICAR ESTADO COLUMNA, DOCUMENTAR CON FOTOS</t>
+          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1164,30 +1164,30 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 4154, "cod_calle": 18005, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.481018", "y": "-34.563694"}, "direccion": "QUESADA 4154, CABA", "nombre_calle": "QUESADA", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 1887, "cod_calle": 10014, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.394228", "y": "-34.593596"}, "direccion": "JUNCAL 1887, CABA", "nombre_calle": "JUNCAL", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-58.481018</v>
+        <v>-58.394228</v>
       </c>
       <c r="L12" t="n">
-        <v>-34.563694</v>
+        <v>-34.593596</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">9153 </t>
+          <t xml:space="preserve">10051 </t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1197,11 +1197,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ALVAREZ THOMAS AV. 1720</t>
+          <t>MOSCONI GENERAL AV. 2362</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
+          <t>NORMALIZAR CABLES EN DESUSO Y A BAJA ALTURA</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1228,18 +1228,18 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 1720, "cod_calle": 1059, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.466347", "y": "-34.579162"}, "direccion": "ALVAREZ THOMAS AV. 1720, CABA", "nombre_calle": "ALVAREZ THOMAS AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 2362, "cod_calle": 13135, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.495996", "y": "-34.582554"}, "direccion": "MOSCONI GENERAL AV. 2362, CABA", "nombre_calle": "MOSCONI GENERAL AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-58.466347</v>
+        <v>-58.495996</v>
       </c>
       <c r="L13" t="n">
-        <v>-34.579162</v>
+        <v>-34.582554</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1251,21 +1251,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">9158 </t>
+          <t xml:space="preserve">10064 </t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FRANCO 2415</t>
+          <t>CORDOBA AV. 5187</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>MORMALIZAR TENDIDO A BAJA ALTURA</t>
+          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1292,789 +1292,21 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>{"direccionesNormalizadas": [{"altura": 2415, "cod_calle": 6052, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.501083", "y": "-34.578059"}, "direccion": "FRANCO 2415, CABA", "nombre_calle": "FRANCO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
+          <t>{"direccionesNormalizadas": [{"altura": 5187, "cod_calle": 3165, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.435882", "y": "-34.590339"}, "direccion": "CORDOBA AV. 5187, CABA", "nombre_calle": "CORDOBA AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>-58.501083</v>
+        <v>-58.435882</v>
       </c>
       <c r="L14" t="n">
-        <v>-34.578059</v>
+        <v>-34.590339</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9159 </t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>5/13/2026</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>BAZURCO 2442</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>12</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>PENDIENTE ADMIN</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>NORMALIZAR TENDIDO A BAJA ALTURA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>{"direccionesNormalizadas": [{"altura": 2442, "cod_calle": 2038, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.502043", "y": "-34.577603"}, "direccion": "BAZURCO 2442, CABA", "nombre_calle": "BAZURCO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>-58.502043</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-34.577603</v>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Paternal</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>9160</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>5/13/2026</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>CARACAS 5377</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>12</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>PENDIENTE ADMIN</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>NORMALIZAR RED A BAJA ALTURA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>{"direccionesNormalizadas": [{"altura": 5377, "cod_calle": 3062, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.500199", "y": "-34.576706"}, "direccion": "CARACAS 5377, CABA", "nombre_calle": "CARACAS", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>-58.500199</v>
-      </c>
-      <c r="L16" t="n">
-        <v>-34.576706</v>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Paternal</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9185 </t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>5/13/2026</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>CAMARGO 1157</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>15</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>PENDIENTE ADMIN</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>NORMALIZAR RED A BAJA ALTURA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>{"direccionesNormalizadas": [{"altura": 1157, "cod_calle": 3033, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.445853", "y": "-34.595224"}, "direccion": "CAMARGO 1157, CABA", "nombre_calle": "CAMARGO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>-58.445853</v>
-      </c>
-      <c r="L17" t="n">
-        <v>-34.595224</v>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Paternal</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9188 </t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>5/13/2026</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>BARZANA 1566</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>12</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>PENDIENTE ADMIN</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>NORMALIZAR RED A BAJA ALTURA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>{"direccionesNormalizadas": [{"altura": 1566, "cod_calle": 2023, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.483554", "y": "-34.584619"}, "direccion": "BARZANA 1566, CABA", "nombre_calle": "BARZANA", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>-58.483554</v>
-      </c>
-      <c r="L18" t="n">
-        <v>-34.584619</v>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Paternal</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9190 </t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>5/13/2026</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>14 DE JULIO 1303</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>15</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>PENDIENTE ADMIN</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>NORMALIZAR RED A BAJA ALTURA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>{"direccionesNormalizadas": [{"altura": 1303, "cod_calle": 3102, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.461808", "y": "-34.578166"}, "direccion": "14 DE JULIO 1303, CABA", "nombre_calle": "14 DE JULIO", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>-58.461808</v>
-      </c>
-      <c r="L19" t="n">
-        <v>-34.578166</v>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Colegiales</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">900009976010 </t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>5/13/2026</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>JUNCAL 1887</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>3</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>PENDIENTE ADMIN</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>{"direccionesNormalizadas": [{"altura": 1887, "cod_calle": 10014, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.394228", "y": "-34.593596"}, "direccion": "JUNCAL 1887, CABA", "nombre_calle": "JUNCAL", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>-58.394228</v>
-      </c>
-      <c r="L20" t="n">
-        <v>-34.593596</v>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Recoleta</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9922 </t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>5/13/2026</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>ESTADO DE PALESTINA 1014</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>5</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>PENDIENTE ADMIN</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>{"direccionesNormalizadas": [{"altura": 1014, "cod_calle": 19016, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.425117", "y": "-34.598984"}, "direccion": "ESTADO DE PALESTINA 1014, CABA", "nombre_calle": "ESTADO DE PALESTINA", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>-58.425117</v>
-      </c>
-      <c r="L21" t="n">
-        <v>-34.598984</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Almagro</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9990 </t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>5/13/2026</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>COPAHUE 2065</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>4</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>PENDIENTE ADMIN</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>{"direccionesNormalizadas": [{"altura": 2065, "cod_calle": 3162, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.379683", "y": "-34.641191"}, "direccion": "COPAHUE 2065, CABA", "nombre_calle": "COPAHUE", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>-58.379683</v>
-      </c>
-      <c r="L22" t="n">
-        <v>-34.641191</v>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>San Telmo</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7789 </t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>5/14/2026</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>TAGLE 2640</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>14</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>PENDIENTE ADMIN</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>{"direccionesNormalizadas": [{"altura": 2640, "cod_calle": 21006, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.399601", "y": "-34.583071"}, "direccion": "TAGLE 2640, CABA", "nombre_calle": "TAGLE", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>-58.399601</v>
-      </c>
-      <c r="L23" t="n">
-        <v>-34.583071</v>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Recoleta</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7993 </t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>5/14/2026</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>PUEYRREDON AV. 394</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>3</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>PENDIENTE ADMIN</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>{"direccionesNormalizadas": [{"altura": 394, "cod_calle": 17132, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.405850", "y": "-34.605697"}, "direccion": "PUEYRREDON AV. 394, CABA", "nombre_calle": "PUEYRREDON AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}, {"altura": 394, "cod_calle": 17133, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.440806", "y": "-34.615134"}, "direccion": "PUEYRREDON, HONORIO, DR. AV. 394, CABA", "nombre_calle": "PUEYRREDON, HONORIO, DR. AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>-58.40585</v>
-      </c>
-      <c r="L24" t="n">
-        <v>-34.605697</v>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Almagro</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10051 </t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>5/14/2026</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>MOSCONI GENERAL AV. 2362</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>12</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>PENDIENTE ADMIN</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>NORMALIZAR CABLES EN DESUSO Y A BAJA ALTURA</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>{"direccionesNormalizadas": [{"altura": 2362, "cod_calle": 13135, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.495996", "y": "-34.582554"}, "direccion": "MOSCONI GENERAL AV. 2362, CABA", "nombre_calle": "MOSCONI GENERAL AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>-58.495996</v>
-      </c>
-      <c r="L25" t="n">
-        <v>-34.582554</v>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Paternal</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10064 </t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>5/14/2026</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>CORDOBA AV. 5187</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>14</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>PENDIENTE ADMIN</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>NORMALIZAR CABLES A BAJA ALTURA</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>{"direccionesNormalizadas": [{"altura": 5187, "cod_calle": 3165, "cod_calle_cruce": null, "cod_partido": "caba", "coordenadas": {"srid": 4326, "x": "-58.435882", "y": "-34.590339"}, "direccion": "CORDOBA AV. 5187, CABA", "nombre_calle": "CORDOBA AV.", "nombre_calle_cruce": "", "nombre_localidad": "CABA", "nombre_partido": "CABA", "tipo": "calle_altura"}]}</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
-        <v>-58.435882</v>
-      </c>
-      <c r="L26" t="n">
-        <v>-34.590339</v>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
         <is>
           <t>Capital Sur</t>
         </is>
